--- a/filer/32931499_sun.xlsx
+++ b/filer/32931499_sun.xlsx
@@ -648,7 +648,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.)</t>
+          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.) · Klasse B · Udvidet gennemgang · Regnskabsår 1/11–31/10 (forskudt)</t>
         </is>
       </c>
     </row>

--- a/filer/32931499_sun.xlsx
+++ b/filer/32931499_sun.xlsx
@@ -628,7 +628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L84"/>
+  <dimension ref="A1:L86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -662,7 +662,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Indekstal (2020=100)</t>
+          <t>Indekstal (2021=100)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -677,35 +677,35 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
@@ -1531,35 +1531,35 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
@@ -2481,35 +2481,35 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="44" ht="16" customHeight="1">
@@ -3671,19 +3671,19 @@
         </is>
       </c>
       <c r="B69" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C69" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="70" ht="16" customHeight="1">
@@ -3789,19 +3789,19 @@
         </is>
       </c>
       <c r="B73" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C73" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="74" ht="16" customHeight="1">
@@ -4099,6 +4099,13 @@
       <c r="F84" s="13">
         <f>IFERROR($F$29/($F$50+$F$53)*100,"")</f>
         <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="15" t="inlineStr">
+        <is>
+          <t>Pengestrømsopgørelse ikke offentliggjort (jf. koncernfritagelse, ÅRL §86, stk. 4)</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -4130,19 +4137,19 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
@@ -4200,19 +4207,19 @@
         </is>
       </c>
       <c r="B6" s="16" t="n">
-        <v>15537</v>
+        <v>12322</v>
       </c>
       <c r="C6" s="16" t="n">
-        <v>12322</v>
+        <v>19587</v>
       </c>
       <c r="D6" s="16" t="n">
-        <v>19587</v>
+        <v>24223</v>
       </c>
       <c r="E6" s="16" t="n">
-        <v>24223</v>
+        <v>30278</v>
       </c>
       <c r="F6" s="16" t="n">
-        <v>30278</v>
+        <v>22885</v>
       </c>
     </row>
     <row r="7">
@@ -4222,19 +4229,19 @@
         </is>
       </c>
       <c r="B7" s="16" t="n">
-        <v>11054</v>
+        <v>7044</v>
       </c>
       <c r="C7" s="16" t="n">
-        <v>7044</v>
+        <v>8383</v>
       </c>
       <c r="D7" s="16" t="n">
-        <v>8383</v>
+        <v>10904</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>10904</v>
+        <v>11593</v>
       </c>
       <c r="F7" s="16" t="n">
-        <v>11593</v>
+        <v>15782</v>
       </c>
     </row>
     <row r="8">
@@ -4251,19 +4258,19 @@
         </is>
       </c>
       <c r="B9" s="16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C9" s="16" t="n">
         <v>0</v>
       </c>
       <c r="D9" s="16" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="F9" s="16" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10">
@@ -4273,16 +4280,16 @@
         </is>
       </c>
       <c r="B10" s="16" t="n"/>
-      <c r="C10" s="16" t="n"/>
+      <c r="C10" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="D10" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="E10" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="16" t="n">
-        <v>15</v>
-      </c>
-      <c r="F10" s="16" t="n">
-        <v>0</v>
-      </c>
+      <c r="F10" s="16" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="17" t="inlineStr">
@@ -4291,19 +4298,19 @@
         </is>
       </c>
       <c r="B11" s="16" t="n">
-        <v>4482</v>
+        <v>5279</v>
       </c>
       <c r="C11" s="16" t="n">
-        <v>5279</v>
+        <v>11204</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>11204</v>
+        <v>13292</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>13292</v>
+        <v>18653</v>
       </c>
       <c r="F11" s="16" t="n">
-        <v>18653</v>
+        <v>7067</v>
       </c>
     </row>
     <row r="12">
@@ -4325,19 +4332,19 @@
         </is>
       </c>
       <c r="B13" s="16" t="n">
-        <v>2701</v>
+        <v>145</v>
       </c>
       <c r="C13" s="16" t="n">
-        <v>145</v>
+        <v>601</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>601</v>
+        <v>3158</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>3158</v>
+        <v>6033</v>
       </c>
       <c r="F13" s="16" t="n">
-        <v>6033</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="14">
@@ -4350,7 +4357,9 @@
       <c r="C14" s="16" t="n"/>
       <c r="D14" s="16" t="n"/>
       <c r="E14" s="16" t="n"/>
-      <c r="F14" s="16" t="n"/>
+      <c r="F14" s="16" t="n">
+        <v>5619</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="17" t="inlineStr">
@@ -4371,19 +4380,19 @@
         </is>
       </c>
       <c r="B16" s="16" t="n">
-        <v>5761</v>
+        <v>2600</v>
       </c>
       <c r="C16" s="16" t="n">
-        <v>2600</v>
+        <v>8334</v>
       </c>
       <c r="D16" s="16" t="n">
-        <v>8334</v>
+        <v>12583</v>
       </c>
       <c r="E16" s="16" t="n">
-        <v>12583</v>
+        <v>18877</v>
       </c>
       <c r="F16" s="16" t="n">
-        <v>18877</v>
+        <v>2866</v>
       </c>
     </row>
     <row r="17">
@@ -4393,19 +4402,19 @@
         </is>
       </c>
       <c r="B17" s="16" t="n">
-        <v>1759</v>
+        <v>103</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>103</v>
+        <v>1883</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>1883</v>
+        <v>2757</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>2757</v>
+        <v>4177</v>
       </c>
       <c r="F17" s="16" t="n">
-        <v>4177</v>
+        <v>650</v>
       </c>
     </row>
     <row r="18">
@@ -4415,19 +4424,19 @@
         </is>
       </c>
       <c r="B18" s="16" t="n">
-        <v>4002</v>
+        <v>2497</v>
       </c>
       <c r="C18" s="16" t="n">
-        <v>2497</v>
+        <v>6451</v>
       </c>
       <c r="D18" s="16" t="n">
-        <v>6451</v>
+        <v>9826</v>
       </c>
       <c r="E18" s="16" t="n">
-        <v>9826</v>
+        <v>14699</v>
       </c>
       <c r="F18" s="16" t="n">
-        <v>14699</v>
+        <v>2216</v>
       </c>
     </row>
     <row r="19">
@@ -4437,19 +4446,19 @@
         </is>
       </c>
       <c r="B19" s="16" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C19" s="16" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D19" s="16" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F19" s="16" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4493,19 +4502,19 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
@@ -4545,13 +4554,13 @@
         <v>0</v>
       </c>
       <c r="D4" s="16" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="E4" s="16" t="n">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="F4" s="16" t="n">
-        <v>116</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5">
@@ -4591,13 +4600,13 @@
         <v>0</v>
       </c>
       <c r="D7" s="16" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="F7" s="16" t="n">
-        <v>116</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8">
@@ -4613,13 +4622,13 @@
         <v>0</v>
       </c>
       <c r="D8" s="16" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>116</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9">
@@ -4631,16 +4640,14 @@
       <c r="B9" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C9" s="16" t="n"/>
+      <c r="D9" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="16" t="n"/>
       <c r="E9" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="16" t="n">
-        <v>0</v>
-      </c>
+      <c r="F9" s="16" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
@@ -4649,19 +4656,19 @@
         </is>
       </c>
       <c r="B10" s="16" t="n">
-        <v>54957</v>
+        <v>55552</v>
       </c>
       <c r="C10" s="16" t="n">
-        <v>55552</v>
+        <v>55804</v>
       </c>
       <c r="D10" s="16" t="n">
-        <v>55804</v>
+        <v>62007</v>
       </c>
       <c r="E10" s="16" t="n">
-        <v>62007</v>
+        <v>64981</v>
       </c>
       <c r="F10" s="16" t="n">
-        <v>64981</v>
+        <v>29399</v>
       </c>
     </row>
     <row r="11">
@@ -4671,19 +4678,19 @@
         </is>
       </c>
       <c r="B11" s="16" t="n">
-        <v>708</v>
+        <v>1046</v>
       </c>
       <c r="C11" s="16" t="n">
-        <v>1046</v>
+        <v>1346</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>1346</v>
+        <v>1195</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>1195</v>
+        <v>2419</v>
       </c>
       <c r="F11" s="16" t="n">
-        <v>2419</v>
+        <v>3109</v>
       </c>
     </row>
     <row r="12">
@@ -4693,19 +4700,19 @@
         </is>
       </c>
       <c r="B12" s="16" t="n">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="C12" s="16" t="n">
-        <v>39</v>
+        <v>118</v>
       </c>
       <c r="D12" s="16" t="n">
-        <v>118</v>
+        <v>70</v>
       </c>
       <c r="E12" s="16" t="n">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="F12" s="16" t="n">
-        <v>35</v>
+        <v>6597</v>
       </c>
     </row>
     <row r="13">
@@ -4715,20 +4722,18 @@
         </is>
       </c>
       <c r="B13" s="16" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C13" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="E13" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="16" t="n">
-        <v>6</v>
-      </c>
-      <c r="F13" s="16" t="n">
-        <v>0</v>
-      </c>
+      <c r="F13" s="16" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
@@ -4761,19 +4766,19 @@
         </is>
       </c>
       <c r="B16" s="16" t="n">
-        <v>55699</v>
+        <v>56643</v>
       </c>
       <c r="C16" s="16" t="n">
-        <v>56643</v>
+        <v>57268</v>
       </c>
       <c r="D16" s="16" t="n">
-        <v>57268</v>
+        <v>63278</v>
       </c>
       <c r="E16" s="16" t="n">
-        <v>63278</v>
+        <v>67435</v>
       </c>
       <c r="F16" s="16" t="n">
-        <v>67435</v>
+        <v>39105</v>
       </c>
     </row>
     <row r="17">
@@ -4795,19 +4800,19 @@
         </is>
       </c>
       <c r="B18" s="16" t="n">
-        <v>13995</v>
+        <v>8284</v>
       </c>
       <c r="C18" s="16" t="n">
-        <v>8284</v>
+        <v>6280</v>
       </c>
       <c r="D18" s="16" t="n">
-        <v>6280</v>
+        <v>4989</v>
       </c>
       <c r="E18" s="16" t="n">
-        <v>4989</v>
+        <v>2677</v>
       </c>
       <c r="F18" s="16" t="n">
-        <v>2677</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="19">
@@ -4817,19 +4822,19 @@
         </is>
       </c>
       <c r="B19" s="16" t="n">
-        <v>69694</v>
+        <v>64927</v>
       </c>
       <c r="C19" s="16" t="n">
-        <v>64927</v>
+        <v>63548</v>
       </c>
       <c r="D19" s="16" t="n">
-        <v>63548</v>
+        <v>68267</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>68267</v>
+        <v>70111</v>
       </c>
       <c r="F19" s="16" t="n">
-        <v>70111</v>
+        <v>40457</v>
       </c>
     </row>
     <row r="20">
@@ -4839,19 +4844,19 @@
         </is>
       </c>
       <c r="B20" s="16" t="n">
-        <v>69694</v>
+        <v>64927</v>
       </c>
       <c r="C20" s="16" t="n">
-        <v>64927</v>
+        <v>63548</v>
       </c>
       <c r="D20" s="16" t="n">
-        <v>63548</v>
+        <v>68406</v>
       </c>
       <c r="E20" s="16" t="n">
-        <v>68406</v>
+        <v>70228</v>
       </c>
       <c r="F20" s="16" t="n">
-        <v>70228</v>
+        <v>40538</v>
       </c>
     </row>
     <row r="21">
@@ -4931,19 +4936,19 @@
         </is>
       </c>
       <c r="B26" s="16" t="n">
-        <v>28274</v>
+        <v>30770</v>
       </c>
       <c r="C26" s="16" t="n">
-        <v>30770</v>
+        <v>37221</v>
       </c>
       <c r="D26" s="16" t="n">
-        <v>37221</v>
+        <v>47047</v>
       </c>
       <c r="E26" s="16" t="n">
-        <v>47047</v>
+        <v>1746</v>
       </c>
       <c r="F26" s="16" t="n">
-        <v>1746</v>
+        <v>3962</v>
       </c>
     </row>
     <row r="27">
@@ -4953,19 +4958,19 @@
         </is>
       </c>
       <c r="B27" s="16" t="n">
-        <v>28774</v>
+        <v>31270</v>
       </c>
       <c r="C27" s="16" t="n">
-        <v>31270</v>
+        <v>37721</v>
       </c>
       <c r="D27" s="16" t="n">
-        <v>37721</v>
+        <v>47547</v>
       </c>
       <c r="E27" s="16" t="n">
-        <v>47547</v>
+        <v>62246</v>
       </c>
       <c r="F27" s="16" t="n">
-        <v>62246</v>
+        <v>4462</v>
       </c>
     </row>
     <row r="28">
@@ -4976,12 +4981,14 @@
       </c>
       <c r="B28" s="16" t="n"/>
       <c r="C28" s="16" t="n"/>
-      <c r="D28" s="16" t="n"/>
+      <c r="D28" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F28" s="16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -4991,17 +4998,17 @@
         </is>
       </c>
       <c r="B29" s="16" t="n">
-        <v>2219</v>
-      </c>
-      <c r="C29" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D29" s="16" t="n"/>
+      <c r="C29" s="16" t="n"/>
+      <c r="D29" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F29" s="16" t="n">
-        <v>5</v>
+        <v>231</v>
       </c>
     </row>
     <row r="30">
@@ -5011,19 +5018,19 @@
         </is>
       </c>
       <c r="B30" s="16" t="n">
-        <v>1519</v>
+        <v>0</v>
       </c>
       <c r="C30" s="16" t="n">
-        <v>0</v>
+        <v>1473</v>
       </c>
       <c r="D30" s="16" t="n">
-        <v>1473</v>
+        <v>2467</v>
       </c>
       <c r="E30" s="16" t="n">
-        <v>2467</v>
+        <v>3856</v>
       </c>
       <c r="F30" s="16" t="n">
-        <v>3856</v>
+        <v>259</v>
       </c>
     </row>
     <row r="31">
@@ -5056,15 +5063,17 @@
           <t>Kreditinstitutter</t>
         </is>
       </c>
-      <c r="B33" s="16" t="n"/>
+      <c r="B33" s="16" t="n">
+        <v>274</v>
+      </c>
       <c r="C33" s="16" t="n">
-        <v>274</v>
-      </c>
-      <c r="D33" s="16" t="n">
         <v>18620</v>
       </c>
+      <c r="D33" s="16" t="n"/>
       <c r="E33" s="16" t="n"/>
-      <c r="F33" s="16" t="n"/>
+      <c r="F33" s="16" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="15" t="inlineStr">
@@ -5085,19 +5094,19 @@
         </is>
       </c>
       <c r="B35" s="16" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C35" s="16" t="n">
-        <v>49</v>
+        <v>535</v>
       </c>
       <c r="D35" s="16" t="n">
-        <v>535</v>
+        <v>1155</v>
       </c>
       <c r="E35" s="16" t="n">
-        <v>1155</v>
+        <v>140</v>
       </c>
       <c r="F35" s="16" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="36">
@@ -5107,19 +5116,19 @@
         </is>
       </c>
       <c r="B36" s="16" t="n">
-        <v>18600</v>
+        <v>30338</v>
       </c>
       <c r="C36" s="16" t="n">
-        <v>30338</v>
+        <v>4223</v>
       </c>
       <c r="D36" s="16" t="n">
-        <v>4223</v>
+        <v>12530</v>
       </c>
       <c r="E36" s="16" t="n">
-        <v>12530</v>
+        <v>2541</v>
       </c>
       <c r="F36" s="16" t="n">
-        <v>2541</v>
+        <v>34678</v>
       </c>
     </row>
     <row r="37">
@@ -5141,19 +5150,19 @@
         </is>
       </c>
       <c r="B38" s="16" t="n">
-        <v>193</v>
+        <v>1284</v>
       </c>
       <c r="C38" s="16" t="n">
-        <v>1284</v>
+        <v>0</v>
       </c>
       <c r="D38" s="16" t="n">
+        <v>1069</v>
+      </c>
+      <c r="E38" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="E38" s="16" t="n">
-        <v>1069</v>
-      </c>
       <c r="F38" s="16" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
     </row>
     <row r="39">
@@ -5175,19 +5184,19 @@
         </is>
       </c>
       <c r="B40" s="16" t="n">
-        <v>2183</v>
+        <v>1631</v>
       </c>
       <c r="C40" s="16" t="n">
-        <v>1631</v>
+        <v>900</v>
       </c>
       <c r="D40" s="16" t="n">
-        <v>900</v>
+        <v>3566</v>
       </c>
       <c r="E40" s="16" t="n">
-        <v>3566</v>
+        <v>1240</v>
       </c>
       <c r="F40" s="16" t="n">
-        <v>1240</v>
+        <v>715</v>
       </c>
     </row>
     <row r="41">
@@ -5197,19 +5206,19 @@
         </is>
       </c>
       <c r="B41" s="16" t="n">
-        <v>16160</v>
+        <v>81</v>
       </c>
       <c r="C41" s="16" t="n">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D41" s="16" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="E41" s="16" t="n">
+        <v>170</v>
+      </c>
+      <c r="F41" s="16" t="n">
         <v>0</v>
-      </c>
-      <c r="F41" s="16" t="n">
-        <v>170</v>
       </c>
     </row>
     <row r="42">
@@ -5219,19 +5228,19 @@
         </is>
       </c>
       <c r="B42" s="16" t="n">
-        <v>37181</v>
+        <v>33656</v>
       </c>
       <c r="C42" s="16" t="n">
-        <v>33656</v>
+        <v>24354</v>
       </c>
       <c r="D42" s="16" t="n">
-        <v>24354</v>
+        <v>18392</v>
       </c>
       <c r="E42" s="16" t="n">
-        <v>18392</v>
+        <v>4120</v>
       </c>
       <c r="F42" s="16" t="n">
-        <v>4120</v>
+        <v>35586</v>
       </c>
     </row>
     <row r="43">
@@ -5241,19 +5250,19 @@
         </is>
       </c>
       <c r="B43" s="16" t="n">
-        <v>38700</v>
+        <v>33656</v>
       </c>
       <c r="C43" s="16" t="n">
-        <v>33656</v>
+        <v>25827</v>
       </c>
       <c r="D43" s="16" t="n">
-        <v>25827</v>
+        <v>20859</v>
       </c>
       <c r="E43" s="16" t="n">
-        <v>20859</v>
+        <v>7976</v>
       </c>
       <c r="F43" s="16" t="n">
-        <v>7976</v>
+        <v>35845</v>
       </c>
     </row>
     <row r="44">
@@ -5263,19 +5272,19 @@
         </is>
       </c>
       <c r="B44" s="16" t="n">
-        <v>69694</v>
+        <v>64927</v>
       </c>
       <c r="C44" s="16" t="n">
-        <v>64927</v>
+        <v>63548</v>
       </c>
       <c r="D44" s="16" t="n">
-        <v>63548</v>
+        <v>68406</v>
       </c>
       <c r="E44" s="16" t="n">
-        <v>68406</v>
+        <v>70228</v>
       </c>
       <c r="F44" s="16" t="n">
-        <v>70228</v>
+        <v>40538</v>
       </c>
     </row>
   </sheetData>
@@ -5314,13 +5323,13 @@
         </is>
       </c>
       <c r="B3" s="20" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C3" s="20" t="n">
         <v>2024</v>
       </c>
-      <c r="C3" s="20" t="n">
+      <c r="D3" s="20" t="n">
         <v>2023</v>
-      </c>
-      <c r="D3" s="20" t="n">
-        <v>2022</v>
       </c>
       <c r="F3" s="21" t="inlineStr">
         <is>
@@ -6025,7 +6034,7 @@
     <row r="40">
       <c r="A40" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for indtjeningsevne (2022=100)</t>
+          <t>Indekstal for indtjeningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B40" s="22" t="n"/>
@@ -6143,7 +6152,7 @@
     <row r="47">
       <c r="A47" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for kapitaltilpasningsevne (2022=100)</t>
+          <t>Indekstal for kapitaltilpasningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B47" s="22" t="n"/>
@@ -6319,7 +6328,7 @@
     <row r="58">
       <c r="A58" s="32" t="inlineStr">
         <is>
-          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2022-2024. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
+          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2023-2025. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
         </is>
       </c>
       <c r="B58" s="29" t="n"/>
@@ -6542,27 +6551,27 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2020 t.kr.</t>
+          <t>2021 t.kr.</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2021 t.kr.</t>
+          <t>2022 t.kr.</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2022 t.kr.</t>
+          <t>2023 t.kr.</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2023 t.kr.</t>
+          <t>2024 t.kr.</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2024 t.kr.</t>
+          <t>2025 t.kr.</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -6588,20 +6597,18 @@
         </is>
       </c>
       <c r="D3" s="35" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="E3" s="35" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="F3" s="35" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="G3" s="35" t="n">
-        <v>89</v>
-      </c>
-      <c r="H3" s="35" t="n">
         <v>6</v>
       </c>
+      <c r="H3" s="35" t="n"/>
       <c r="I3" s="36" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -6625,19 +6632,19 @@
         </is>
       </c>
       <c r="D4" s="38" t="n">
-        <v>1519</v>
+        <v>0</v>
       </c>
       <c r="E4" s="38" t="n">
-        <v>0</v>
+        <v>1473</v>
       </c>
       <c r="F4" s="38" t="n">
-        <v>1473</v>
+        <v>2467</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>2467</v>
+        <v>3856</v>
       </c>
       <c r="H4" s="38" t="n">
-        <v>3856</v>
+        <v>259</v>
       </c>
       <c r="I4" s="39" t="inlineStr">
         <is>
